--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N16_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>119.6138868345018</v>
+        <v>19.43725661060655</v>
       </c>
       <c r="D2" t="n">
-        <v>119.6136981584173</v>
+        <v>19.43722595074281</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
